--- a/output/北塩原村_現行計画評価.xlsx
+++ b/output/北塩原村_現行計画評価.xlsx
@@ -2825,7 +2825,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0728調査票での対応</t>
+          <t>確定版調査票での対応</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>問37「障がいがあることで差別や偏見を感じたことはありますか」</t>
+          <t>確定版 問34（障がい児版は問33）。0728版の問37から番号が変更</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>問32「いま利用している福祉サービスに満足していますか」</t>
+          <t>確定版 問30。0728版の問32から番号が変更</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -3096,7 +3096,8 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>⑦スポーツ・文化</t>
+          <t>⑦スポーツ・文化
+（本編は④教育・育成(2)生涯学習に掲げ、⑦で再掲）</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -3106,7 +3107,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>28.1％（趣味・スポーツ15.3％＋グループ活動12.8％、令和5年度）</t>
+          <t>28.1％（令和5年度。本編は趣味・スポーツ15.3％＋グループ活動12.8％と記載）／前回調査報告書 問17は趣味やスポーツ16.3％であり計29.1％になる（転記誤りと考えられる）</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -3121,7 +3122,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>**該当設問なし**（問13は外出頻度、問14は困ること、問15は移動手段）</t>
+          <t>該当設問なし（確定版は問12が外出頻度、問13が移動手段、問14が困ること）</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
@@ -4261,7 +4262,7 @@
       <c r="D19" s="26" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>今回は障がい者版52問・障がい児版51問</t>
+          <t>今回は障がい者版49問・障がい児版47問（令和8年8月25日 確定版）</t>
         </is>
       </c>
     </row>
